--- a/artfynd/A 32758-2025 artfynd.xlsx
+++ b/artfynd/A 32758-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112327072</v>
+        <v>112327480</v>
       </c>
       <c r="B2" t="n">
-        <v>56477</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,29 +686,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fjällberget, Ly lm</t>
@@ -787,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112327034</v>
+        <v>112327326</v>
       </c>
       <c r="B3" t="n">
-        <v>96803</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,7 +812,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>642147</v>
+        <v>642157</v>
       </c>
       <c r="R3" t="n">
         <v>7163079</v>
@@ -897,16 +882,11 @@
         <v>112327329</v>
       </c>
       <c r="B4" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1001,19 +981,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112327335</v>
+        <v>112327332</v>
       </c>
       <c r="B5" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1041,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>642093</v>
+        <v>642012</v>
       </c>
       <c r="R5" t="n">
-        <v>7163080</v>
+        <v>7163079</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1090,7 +1065,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>Oskar Wallströmer</t>
+          <t>Astrid Hedman</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1108,19 +1083,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112327326</v>
+        <v>112327334</v>
       </c>
       <c r="B6" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1148,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>642157</v>
+        <v>641983</v>
       </c>
       <c r="R6" t="n">
-        <v>7163080</v>
+        <v>7163079</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1215,19 +1185,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112327334</v>
+        <v>112327335</v>
       </c>
       <c r="B7" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1255,7 +1220,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>641983</v>
+        <v>642093</v>
       </c>
       <c r="R7" t="n">
         <v>7163079</v>
@@ -1304,7 +1269,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>Astrid Hedman</t>
+          <t>Oskar Wallströmer</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1322,37 +1287,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112327579</v>
+        <v>112327336</v>
       </c>
       <c r="B8" t="n">
-        <v>96700</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>642089</v>
+        <v>642100</v>
       </c>
       <c r="R8" t="n">
-        <v>7163078</v>
+        <v>7163079</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1429,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112327037</v>
+        <v>112327072</v>
       </c>
       <c r="B9" t="n">
-        <v>96803</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,31 +1400,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjällberget, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>642092</v>
+        <v>641982</v>
       </c>
       <c r="R9" t="n">
         <v>7163079</v>
@@ -1518,7 +1478,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>Oskar Wallströmer</t>
+          <t>Astrid Hedman</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1536,37 +1496,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112327336</v>
+        <v>112327579</v>
       </c>
       <c r="B10" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,7 +1531,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>642100</v>
+        <v>642089</v>
       </c>
       <c r="R10" t="n">
         <v>7163079</v>
@@ -1643,37 +1598,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112327332</v>
+        <v>112327126</v>
       </c>
       <c r="B11" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>642012</v>
+        <v>642092</v>
       </c>
       <c r="R11" t="n">
-        <v>7163080</v>
+        <v>7163079</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1732,7 +1682,7 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>Astrid Hedman</t>
+          <t>Oskar Wallströmer</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1750,37 +1700,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112327480</v>
+        <v>112327034</v>
       </c>
       <c r="B12" t="n">
-        <v>81426</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,7 +1735,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>641982</v>
+        <v>642147</v>
       </c>
       <c r="R12" t="n">
         <v>7163079</v>
@@ -1857,15 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112327126</v>
+        <v>112327037</v>
       </c>
       <c r="B13" t="n">
-        <v>95748</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1961,414 +1901,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>121530502</v>
-      </c>
-      <c r="B14" t="n">
-        <v>98030</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>219790</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Fjällberget, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>642089</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7163079</v>
-      </c>
-      <c r="S14" t="n">
-        <v>50</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Max Jonsson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Max Jonsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>121530237</v>
-      </c>
-      <c r="B15" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Fjällberget, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>642157</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7163079</v>
-      </c>
-      <c r="S15" t="n">
-        <v>50</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Max Jonsson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Max Jonsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>121530245</v>
-      </c>
-      <c r="B16" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Fjällberget, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>642093</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7163079</v>
-      </c>
-      <c r="S16" t="n">
-        <v>50</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Max Jonsson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Max Jonsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>121530243</v>
-      </c>
-      <c r="B17" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Fjällberget, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>642012</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7163079</v>
-      </c>
-      <c r="S17" t="n">
-        <v>50</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Max Jonsson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Max Jonsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
